--- a/summary output/summary all_but_cafri  14oct2025.xlsx
+++ b/summary output/summary all_but_cafri  14oct2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjs23\Documents\R\slash-wall-vegetation\summary output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC5C3F9-C0D3-429F-B5DB-356C374B1A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C0867E-C22C-4E10-8CCC-71E1789B7D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="678" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="top species" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,20 @@
     <sheet name="full_spp_list" sheetId="5" r:id="rId7"/>
     <sheet name="type_list" sheetId="6" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -560,6 +573,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -568,9 +584,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -19010,44 +19023,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
     </row>
     <row r="2" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="12" t="s">
@@ -20963,44 +20976,44 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="16"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="16"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="G46" s="12" t="s">
@@ -26418,21 +26431,21 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="H3" s="18" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="H3" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="16" t="s">
         <v>121</v>
       </c>
       <c r="B4" s="6" t="s">
